--- a/tools/excel/netherlands/abdo_2019.xlsx
+++ b/tools/excel/netherlands/abdo_2019.xlsx
@@ -852,8 +852,8 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The Contractor satisfies the ABDO 2017 requirements with regard to the
-Classified Contract in question..</t>
+          <t>The Contractor satisfies the ABDO 2019 requirements with regard to the
+Classified Contract in question.</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
         <is>
           <t>The Contractor has unequivocally implemented in its
 organisation the measures and procedures described in the
-security plan..</t>
+security plan.</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>The SO instructs employees tasked with carrying out an SC on ABDO 2017
+          <t>The SO instructs employees tasked with carrying out an SC on ABDO 2019
 procedures and their corresponding responsibilities on appointment to a
 Confidential Position, at the start of a new SC and subsequently
 periodically, i.e. at least once a year.</t>
@@ -2380,7 +2380,7 @@
       <c r="I45" t="inlineStr">
         <is>
           <t>Once permission for outsourcing to the Subcontractor has been
-granted by DISS/ISO, the Contractor incorporates the ABDO 2017 in its
+granted by DISS/ISO, the Contractor incorporates the ABDO 2019 in its
 contract with the Subcontractors coming into contact with an IBP. The
 Contractor submits to DISS/ISO a completed SCC in this regard.</t>
         </is>
@@ -2460,7 +2460,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The Contractor stipulates the ABDO 2017 to its suppliers of system
+          <t>The Contractor stipulates the ABDO 2019 to its suppliers of system
 components requiring a certain degree of protection due to their
 critical/vital function.</t>
         </is>
@@ -2503,7 +2503,7 @@
           <t>When companies work on an SC in partnership with other companies, any
 work on an IBP is centralised as far as is possible.
 (The Contractor bears responsibility for compliance with the requirements of
-the ABDO 2017 by any company it takes under its wing as a Subcontractor).</t>
+the ABDO 2019 by any company it takes under its wing as a Subcontractor).</t>
         </is>
       </c>
     </row>
